--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -26,7 +26,7 @@
     <t>EndJump</t>
   </si>
   <si>
-    <t>Ending</t>
+    <t>Event1</t>
   </si>
   <si>
     <t>なし</t>
@@ -77,8 +77,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -90,11 +90,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -107,7 +129,83 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -122,30 +220,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -154,81 +229,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,13 +243,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -261,49 +405,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -315,115 +417,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,6 +434,32 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -485,21 +511,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -523,17 +534,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -542,145 +542,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1026,17 +1026,17 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" t="str">
         <f>INDEX(Define!B:B,MATCH(C2,Define!A:A))</f>
-        <v>リザルト</v>
+        <v>戦略</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -26,7 +26,7 @@
     <t>EndJump</t>
   </si>
   <si>
-    <t>Event1</t>
+    <t>101_output</t>
   </si>
   <si>
     <t>なし</t>
@@ -76,9 +76,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -91,7 +91,28 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -99,22 +120,68 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -128,36 +195,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -166,6 +203,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -175,60 +221,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,13 +243,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -261,55 +387,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -321,109 +417,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,41 +434,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -483,15 +448,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -534,6 +490,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -542,145 +542,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>Id</t>
   </si>
@@ -27,6 +27,9 @@
   </si>
   <si>
     <t>101_output</t>
+  </si>
+  <si>
+    <t>102_output</t>
   </si>
   <si>
     <t>なし</t>
@@ -91,73 +94,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -171,17 +108,99 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -195,6 +214,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -202,37 +236,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -243,31 +246,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -279,151 +426,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,26 +455,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -491,11 +481,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -511,10 +507,17 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -542,7 +545,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -551,7 +554,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -563,124 +566,124 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1007,8 +1010,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="3"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="13.2727272727273" customWidth="1"/>
   </cols>
@@ -1036,6 +1039,21 @@
       </c>
       <c r="D2" t="str">
         <f>INDEX(Define!B:B,MATCH(C2,Define!A:A))</f>
+        <v>戦略</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>9</v>
+      </c>
+      <c r="D3" t="str">
+        <f>INDEX(Define!B:B,MATCH(C3,Define!A:A))</f>
         <v>戦略</v>
       </c>
     </row>
@@ -1061,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1069,7 +1087,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1077,7 +1095,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1085,7 +1103,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1093,7 +1111,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1101,7 +1119,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1109,7 +1127,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1117,7 +1135,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1125,7 +1143,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1133,7 +1151,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1141,7 +1159,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1149,7 +1167,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1157,7 +1175,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1165,7 +1183,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Adventures.xlsx
+++ b/Assets/Data/Adventures.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Id</t>
   </si>
@@ -30,6 +30,12 @@
   </si>
   <si>
     <t>102_output</t>
+  </si>
+  <si>
+    <t>103_output</t>
+  </si>
+  <si>
+    <t>104_output</t>
   </si>
   <si>
     <t>なし</t>
@@ -79,10 +85,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -94,7 +100,113 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -108,99 +220,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,25 +237,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -246,109 +252,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -360,73 +432,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -455,28 +461,26 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -500,7 +504,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -516,24 +535,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -545,145 +551,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1010,8 +1016,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="2" outlineLevelCol="3"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="13.2727272727273" customWidth="1"/>
   </cols>
@@ -1054,6 +1060,36 @@
       </c>
       <c r="D3" t="str">
         <f>INDEX(Define!B:B,MATCH(C3,Define!A:A))</f>
+        <v>戦略</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4" t="str">
+        <f>INDEX(Define!B:B,MATCH(C4,Define!A:A))</f>
+        <v>戦略</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5" t="str">
+        <f>INDEX(Define!B:B,MATCH(C5,Define!A:A))</f>
         <v>戦略</v>
       </c>
     </row>
@@ -1079,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1087,7 +1123,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1095,7 +1131,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1103,7 +1139,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1111,7 +1147,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1119,7 +1155,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1127,7 +1163,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1135,7 +1171,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1143,7 +1179,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1151,7 +1187,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1159,7 +1195,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1167,7 +1203,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1175,7 +1211,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1183,7 +1219,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
